--- a/artfynd/A 35246-2022 artfynd.xlsx
+++ b/artfynd/A 35246-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35246-2022 artfynd.xlsx
+++ b/artfynd/A 35246-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106962913</v>
+        <v>106962906</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>439848.8484119319</v>
+        <v>439806</v>
       </c>
       <c r="R2" t="n">
-        <v>7053459.837259749</v>
+        <v>7053595</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +751,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106962916</v>
+        <v>106962907</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,11 +816,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>439913.1832423816</v>
+        <v>439590</v>
       </c>
       <c r="R3" t="n">
-        <v>7053491.555212214</v>
+        <v>7053981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -921,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106962911</v>
+        <v>106962908</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +924,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>439593.9567910262</v>
+        <v>439488</v>
       </c>
       <c r="R4" t="n">
-        <v>7053766.444695568</v>
+        <v>7053728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +967,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1046,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106962912</v>
+        <v>106962909</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1034,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1094,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>439591.9050097073</v>
+        <v>439541</v>
       </c>
       <c r="R5" t="n">
-        <v>7053705.510167869</v>
+        <v>7053694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,19 +1077,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1171,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106962925</v>
+        <v>106962911</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1142,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>439443.0814659022</v>
+        <v>439594</v>
       </c>
       <c r="R6" t="n">
-        <v>7053613.547149821</v>
+        <v>7053767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,19 +1187,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1292,15 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106962922</v>
+        <v>106962912</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1254,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1340,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>439318.9964097005</v>
+        <v>439592</v>
       </c>
       <c r="R7" t="n">
-        <v>7053696.922221558</v>
+        <v>7053706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,19 +1297,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1417,15 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106962928</v>
+        <v>106962913</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,11 +1362,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1465,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>439642.4769625509</v>
+        <v>439849</v>
       </c>
       <c r="R8" t="n">
-        <v>7053482.451319449</v>
+        <v>7053460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1498,19 +1403,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1542,15 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106962921</v>
+        <v>106962914</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,7 +1470,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1590,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>439335.8968375787</v>
+        <v>439861</v>
       </c>
       <c r="R9" t="n">
-        <v>7053718.407298831</v>
+        <v>7053448</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1623,19 +1513,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1667,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106962930</v>
+        <v>106962915</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>439971.7396579599</v>
+        <v>439887</v>
       </c>
       <c r="R10" t="n">
-        <v>7053453.503503216</v>
+        <v>7053458</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1744,19 +1619,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1788,15 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106962917</v>
+        <v>106962916</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1684,11 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1832,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>439967.8668092039</v>
+        <v>439913</v>
       </c>
       <c r="R11" t="n">
-        <v>7053531.468345586</v>
+        <v>7053492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1865,19 +1729,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1909,15 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106962909</v>
+        <v>106962917</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,11 +1794,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1957,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>439540.8807714934</v>
+        <v>439968</v>
       </c>
       <c r="R12" t="n">
-        <v>7053694.020409744</v>
+        <v>7053531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1990,19 +1835,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2034,15 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106962915</v>
+        <v>106962921</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +1900,11 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2078,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>439886.7018202743</v>
+        <v>439336</v>
       </c>
       <c r="R13" t="n">
-        <v>7053458.22951703</v>
+        <v>7053718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2111,19 +1945,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2155,15 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106962908</v>
+        <v>106962922</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2203,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>439487.6118737655</v>
+        <v>439319</v>
       </c>
       <c r="R14" t="n">
-        <v>7053728.416207724</v>
+        <v>7053697</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2236,19 +2055,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2283,12 +2092,7 @@
         <v>106962923</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>439443.4798489799</v>
+        <v>439443</v>
       </c>
       <c r="R15" t="n">
-        <v>7053587.724752655</v>
+        <v>7053588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2357,19 +2161,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2404,12 +2198,7 @@
         <v>106962924</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2449,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>439437.3530716728</v>
+        <v>439437</v>
       </c>
       <c r="R16" t="n">
-        <v>7053593.627814571</v>
+        <v>7053594</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2482,19 +2271,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2526,15 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106962914</v>
+        <v>106962925</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2562,11 +2336,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2574,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>439861.1040108867</v>
+        <v>439443</v>
       </c>
       <c r="R17" t="n">
-        <v>7053448.032278429</v>
+        <v>7053614</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2607,19 +2377,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2651,15 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106962927</v>
+        <v>106962926</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2687,11 +2442,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2699,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>439526.6469496049</v>
+        <v>439518</v>
       </c>
       <c r="R18" t="n">
-        <v>7053578.571698579</v>
+        <v>7053580</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2732,19 +2483,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2776,15 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106962926</v>
+        <v>106962927</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2548,11 @@
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2820,10 +2560,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>439518.6446264222</v>
+        <v>439526</v>
       </c>
       <c r="R19" t="n">
-        <v>7053579.614437381</v>
+        <v>7053579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2853,19 +2593,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2897,15 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106962929</v>
+        <v>106962928</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,10 +2670,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>439635.6924185199</v>
+        <v>439643</v>
       </c>
       <c r="R20" t="n">
-        <v>7053477.239236318</v>
+        <v>7053482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2978,19 +2703,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3022,15 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106962906</v>
+        <v>106962929</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3060,7 +2770,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3070,10 +2780,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>439805.9539124641</v>
+        <v>439636</v>
       </c>
       <c r="R21" t="n">
-        <v>7053595.068274091</v>
+        <v>7053477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3103,19 +2813,9 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3144,6 +2844,221 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>106962930</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ny-kaxbodarna Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>439972</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7053453</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>106962931</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ny-kaxbodarna Tångeråsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>439720</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7053335</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35246-2022 artfynd.xlsx
+++ b/artfynd/A 35246-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962907</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962908</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962909</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962913</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962914</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962915</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962916</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962917</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962921</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962922</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2192,6 +2262,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962923</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962924</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2408,6 +2488,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962925</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2514,6 +2599,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962926</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2624,6 +2714,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962927</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2734,6 +2829,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962928</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2844,6 +2944,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962929</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2950,6 +3055,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962930</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3059,8 +3169,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106962931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>